--- a/output/pdf_financials_xlsx/XTRA.xlsx
+++ b/output/pdf_financials_xlsx/XTRA.xlsx
@@ -1196,10 +1196,10 @@
         <v>-0.303263</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6042419999999999</v>
+        <v>-0.6042419999999999</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>7.736822</v>
+        <v>-7.736822</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.985776</v>
@@ -1214,7 +1214,7 @@
         <v>16.73222</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>39.716689</v>
+        <v>-39.716689</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-16.336473</v>
@@ -1254,16 +1254,16 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-23.971552</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0.12</v>
+        <v>-34.983934</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0.332812</v>
+        <v>-50.585602</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.169886</v>
+        <v>-33.294554</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1464,25 +1464,25 @@
         <v>-0.303263</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.6042419999999999</v>
+        <v>-0.6042419999999999</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>7.736822</v>
+        <v>-7.736822</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11.985776</v>
+        <v>-11.985776</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>17.431967</v>
+        <v>-17.431967</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>25.126395</v>
+        <v>-25.126395</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>16.562334</v>
+        <v>-16.562334</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>39.716689</v>
+        <v>-39.716689</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-16.336473</v>
@@ -1620,25 +1620,25 @@
         <v>-0.303263</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.6042419999999999</v>
+        <v>-0.6042419999999999</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>7.736822</v>
+        <v>-7.736822</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>11.985776</v>
+        <v>-11.985776</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>17.431967</v>
+        <v>-17.431967</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>25.126395</v>
+        <v>-25.126395</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>16.562334</v>
+        <v>-16.562334</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>39.716689</v>
+        <v>-39.716689</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-16.336473</v>
@@ -1776,25 +1776,25 @@
         <v>1.010877</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3.3569</v>
+        <v>-3.3569</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>45.510718</v>
+        <v>-45.510718</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>92.198277</v>
+        <v>-92.198277</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>134.092054</v>
+        <v>-134.092054</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>147.802324</v>
+        <v>-147.802324</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>150.566673</v>
+        <v>-150.566673</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>158.866756</v>
+        <v>-158.866756</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>181.516367</v>
@@ -1828,10 +1828,10 @@
         <v>-0.303263</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.6042419999999999</v>
+        <v>-0.6042419999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.736822</v>
+        <v>-7.736822</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>11.985776</v>
@@ -1846,7 +1846,7 @@
         <v>16.73222</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>39.716689</v>
+        <v>-39.716689</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-16.336473</v>
@@ -1932,10 +1932,10 @@
         <v>-0.302987</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.604463</v>
+        <v>-0.604021</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7.736822</v>
+        <v>-7.736822</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>12.02008</v>
@@ -1950,7 +1950,7 @@
         <v>17.712142</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>40.519614</v>
+        <v>-38.913764</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-15.412709</v>
@@ -2020,7 +2020,7 @@
         <v>1637.019524480695</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1119.569442425897</v>
+        <v>-1075.199311231665</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-374.8916143143049</v>
@@ -2054,25 +2054,25 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.6836840566074446</v>
+        <v>199.3163159433926</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.307236317297707</v>
+        <v>198.6927636827023</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>1.015322533411585</v>
+        <v>198.9846774665884</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -2136,13 +2136,13 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1213.106471280062</v>
+        <v>-1213.106471280062</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1530.750155964787</v>
+        <v>-1530.750155964787</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1097.384376828781</v>
+        <v>-1097.384376828781</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>-397.3608231474464</v>
@@ -5279,19 +5279,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.092316</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.24315</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.226444</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.217965</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.193377</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>2.113167</v>
@@ -6592,19 +6592,19 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.023216</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.0425</v>
+        <v>-0.02536</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.04</v>
+        <v>-0.865258</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>0.00155</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -15637,7 +15637,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -16808,7 +16812,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -17346,7 +17354,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -18909,7 +18921,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -33909,7 +33925,11 @@
           <t>Exploration and evaluation assets expenditures – recovery</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -35701,7 +35721,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -37715,7 +37739,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -46376,25 +46404,25 @@
         </is>
       </c>
       <c r="K429" s="5" t="n">
-        <v>7.736822</v>
+        <v>-7.736822</v>
       </c>
       <c r="L429" s="5" t="n">
-        <v>11.985776</v>
+        <v>-11.985776</v>
       </c>
       <c r="M429" s="5" t="n">
-        <v>17.431967</v>
+        <v>-17.431967</v>
       </c>
       <c r="N429" s="5" t="n">
-        <v>25.126395</v>
+        <v>-25.126395</v>
       </c>
       <c r="O429" s="5" t="n">
-        <v>16.562334</v>
+        <v>-16.562334</v>
       </c>
       <c r="P429" s="5" t="n">
-        <v>39.716689</v>
+        <v>-39.716689</v>
       </c>
       <c r="Q429" s="5" t="n">
-        <v>16.336473</v>
+        <v>-16.336473</v>
       </c>
       <c r="R429" t="inlineStr">
         <is>
@@ -50210,10 +50238,10 @@
         </is>
       </c>
       <c r="J472" s="5" t="n">
-        <v>0.6042419999999999</v>
+        <v>-0.6042419999999999</v>
       </c>
       <c r="K472" s="5" t="n">
-        <v>7.736822</v>
+        <v>-7.736822</v>
       </c>
       <c r="L472" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/XTRA.xlsx
+++ b/output/pdf_financials_xlsx/XTRA.xlsx
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.035895</v>
+        <v>0.119914</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.22304</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>6.600000000000001e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -997,13 +997,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.862013</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.481702</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.024934</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>-0.22304</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.414321</v>
+        <v>-0.414387</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.201558</v>
@@ -1837,13 +1837,13 @@
         <v>11.985776</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>17.551967</v>
+        <v>18.41398</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>25.459207</v>
+        <v>25.940909</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>16.73222</v>
+        <v>16.757154</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-39.716689</v>
@@ -1923,7 +1923,7 @@
         <v>-0.2225</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.413889</v>
+        <v>-0.413955</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.201212</v>
@@ -1941,13 +1941,13 @@
         <v>12.02008</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>18.01913</v>
+        <v>18.881143</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>26.715943</v>
+        <v>27.197645</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>17.712142</v>
+        <v>17.737076</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-38.913764</v>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>1289.850109402852</v>
+        <v>1313.106760961046</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1637.019524480695</v>
+        <v>1639.32401395596</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-1075.199311231665</v>
@@ -2168,22 +2168,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.082334</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.451278</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.269304</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.264929</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.101874</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.19509</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>5.184904</v>
@@ -2195,10 +2195,10 @@
         <v>50.637942</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>22.407251</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>9.652493</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>6.277321</v>
@@ -2272,22 +2272,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.082334</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.451278</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.269304</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.264929</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.101874</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.19509</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>5.184904</v>
@@ -2299,10 +2299,10 @@
         <v>50.637942</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>22.407251</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>9.652493</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>6.277321</v>
@@ -2896,19 +2896,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.135014</v>
+        <v>0.05268</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.453291</v>
+        <v>0.002013</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.27447</v>
+        <v>0.005166</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.271153</v>
+        <v>0.006224</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.110792</v>
+        <v>0.008918000000000001</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -2923,10 +2923,10 @@
         <v>0.694114</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>27.385066</v>
+        <v>4.977815</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>10.008068</v>
+        <v>0.355575</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.66865</v>
@@ -6940,22 +6940,22 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.5820419999999999</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.514964</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.367652</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.362672</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.381427</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.28535</v>
       </c>
     </row>
     <row r="125">
@@ -6992,22 +6992,22 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.5820419999999999</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.514964</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.367652</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.362672</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.381427</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.28535</v>
       </c>
     </row>
     <row r="126">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -21144,7 +21144,11 @@
           <t>Lease payments (Note 9)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -22952,7 +22956,11 @@
           <t>Lease payments (Note 9)</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -24574,7 +24582,11 @@
           <t>Lease payments (Note 8)</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -26307,7 +26319,11 @@
           <t>Lease payments (Note 11)</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -29203,7 +29219,11 @@
           <t>Lease payments (Note 13)</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -47426,7 +47446,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -53020,7 +53040,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -55422,7 +55442,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E529" s="5" t="n">

--- a/output/pdf_financials_xlsx/XTRA.xlsx
+++ b/output/pdf_financials_xlsx/XTRA.xlsx
@@ -832,28 +832,28 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>0.12908</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>0.536418</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>1.940015</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>2.838672</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>5.393093</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>4.362471</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>5.284255</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>5.723359</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>0.099629</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.638547</v>
+        <v>2.174965</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>11.985776</v>
@@ -939,7 +939,7 @@
         <v>-0.099629</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-1.638547</v>
+        <v>-2.174965</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-11.985776</v>
@@ -6319,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.163259</v>
       </c>
     </row>
     <row r="113">
@@ -20786,7 +20786,11 @@
           <t>Proceeds from disposal of property, plant and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -45154,7 +45158,11 @@
           <t>Personnel costs</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XTRA.xlsx
+++ b/output/pdf_financials_xlsx/XTRA.xlsx
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.132435</v>
+        <v>-0.143209</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.22304</v>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.010774</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.010774</v>
+        <v>-0.010774</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.132435</v>
+        <v>-0.143209</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.22304</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.132435</v>
+        <v>-0.143209</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.2225</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-7.523270185533032</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-4.830523672883787</v>
@@ -3773,19 +3773,19 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.069799</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.017238</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.402213</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.513843</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.529466</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -3984,13 +3984,13 @@
         <v>0.075346</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.038726</v>
+        <v>0.055964</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.417213</v>
+        <v>0.819426</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.5258429999999999</v>
+        <v>1.039686</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.229109</v>
@@ -4348,13 +4348,13 @@
         <v>0.005122</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.021973</v>
+        <v>0.004735</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.06825000000000001</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.09319</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0.311657</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -6524,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.427955</v>
       </c>
       <c r="P116" s="3" t="n">
         <v>0</v>
@@ -7471,7 +7471,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.064792</v>
+        <v>-0.06779200000000001</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.161976</v>
@@ -22420,7 +22420,11 @@
           <t>Acquisition of intangible assets (Note 8)</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -27235,7 +27239,11 @@
           <t>Deferred tax recovery (Note 20)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -30060,7 +30068,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -34226,7 +34238,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -35840,7 +35856,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -38309,7 +38329,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -38586,7 +38610,11 @@
           <t>Net proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -39781,7 +39809,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E356" s="5" t="n">
         <v>0.010774</v>
       </c>
@@ -40420,7 +40452,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E363" s="5" t="n">
         <v>-0.003</v>
       </c>
@@ -40693,7 +40729,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E366" s="5" t="n">
         <v>0.244109</v>
       </c>
@@ -54247,7 +54287,11 @@
           <t>Deferred income tax recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E516" t="inlineStr">
         <is>
           <t>-</t>
@@ -55818,7 +55862,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E533" s="5" t="n">
         <v>-0.010774</v>
       </c>
